--- a/artfynd/A 27725-2026 artfynd.xlsx
+++ b/artfynd/A 27725-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135023647</v>
+        <v>135031081</v>
       </c>
       <c r="B3" t="n">
         <v>57162</v>
@@ -816,31 +816,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497636</v>
+        <v>497392</v>
       </c>
       <c r="R3" t="n">
-        <v>6621917</v>
+        <v>6621831</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,17 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fjäder från tjädertupp.</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,38 +883,23 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Våtmark med barrträd</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135031081</v>
+        <v>135031156</v>
       </c>
       <c r="B4" t="n">
         <v>57162</v>
@@ -947,7 +930,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -956,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497392</v>
+        <v>497439</v>
       </c>
       <c r="R4" t="n">
-        <v>6621831</v>
+        <v>6621865</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -991,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På hällen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135031156</v>
+        <v>135031182</v>
       </c>
       <c r="B5" t="n">
         <v>57162</v>
@@ -1056,10 +1044,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497439</v>
+        <v>497444</v>
       </c>
       <c r="R5" t="n">
-        <v>6621865</v>
+        <v>6621867</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1103,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,12 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På hällen</t>
+          <t>Spillning och fjäder fr höna</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135031182</v>
+        <v>135031223</v>
       </c>
       <c r="B6" t="n">
         <v>57162</v>
@@ -1173,24 +1175,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1199,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497444</v>
+        <v>497436</v>
       </c>
       <c r="R6" t="n">
-        <v>6621867</v>
+        <v>6621916</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1234,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,12 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillning och fjäder fr höna</t>
+          <t>På häll</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,7 +1264,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135031223</v>
+        <v>135031358</v>
       </c>
       <c r="B7" t="n">
         <v>57162</v>
@@ -1316,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497436</v>
+        <v>497502</v>
       </c>
       <c r="R7" t="n">
-        <v>6621916</v>
+        <v>6621886</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1351,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,12 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På häll</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,7 +1376,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135031358</v>
+        <v>135031428</v>
       </c>
       <c r="B8" t="n">
         <v>57162</v>
@@ -1433,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497502</v>
+        <v>497530</v>
       </c>
       <c r="R8" t="n">
-        <v>6621886</v>
+        <v>6621896</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1468,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,7 +1461,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vid rotvälta</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,7 +1493,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135031428</v>
+        <v>135031854</v>
       </c>
       <c r="B9" t="n">
         <v>57162</v>
@@ -1545,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497530</v>
+        <v>497649</v>
       </c>
       <c r="R9" t="n">
-        <v>6621896</v>
+        <v>6621782</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1580,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,12 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Vid rotvälta</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,7 +1605,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135031854</v>
+        <v>135038922</v>
       </c>
       <c r="B10" t="n">
         <v>57162</v>
@@ -1651,24 +1634,34 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497649</v>
+        <v>497369</v>
       </c>
       <c r="R10" t="n">
-        <v>6621782</v>
+        <v>6622106</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1697,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1707,7 +1700,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sandbad med honfjädrar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,75 +1720,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135038922</v>
+        <v>135031276</v>
       </c>
       <c r="B11" t="n">
-        <v>57162</v>
+        <v>58136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497369</v>
+        <v>497469</v>
       </c>
       <c r="R11" t="n">
-        <v>6622106</v>
+        <v>6621857</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1819,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1829,12 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Sandbad med honfjädrar</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,6 +1828,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1861,38 +1849,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135031276</v>
+        <v>135031098</v>
       </c>
       <c r="B12" t="n">
-        <v>58136</v>
+        <v>58131</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>103023</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1901,13 +1889,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497469</v>
+        <v>497399</v>
       </c>
       <c r="R12" t="n">
-        <v>6621857</v>
+        <v>6621793</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1936,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1946,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135031098</v>
+        <v>135031702</v>
       </c>
       <c r="B13" t="n">
-        <v>58131</v>
+        <v>8449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,42 +1977,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103023</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497399</v>
+        <v>497612</v>
       </c>
       <c r="R13" t="n">
-        <v>6621793</v>
+        <v>6621778</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2053,7 +2041,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,7 +2051,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,59 +2067,54 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135031702</v>
+        <v>135031097</v>
       </c>
       <c r="B14" t="n">
-        <v>8449</v>
+        <v>56706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>206046</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2135,10 +2123,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497612</v>
+        <v>497411</v>
       </c>
       <c r="R14" t="n">
-        <v>6621778</v>
+        <v>6621836</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2170,7 +2158,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2180,12 +2168,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2212,53 +2195,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135031097</v>
+        <v>134232854</v>
       </c>
       <c r="B15" t="n">
-        <v>56706</v>
+        <v>98060</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206046</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497411</v>
+        <v>497332</v>
       </c>
       <c r="R15" t="n">
-        <v>6621836</v>
+        <v>6621841</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2282,22 +2264,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,131 +2299,15 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>134232854</v>
-      </c>
-      <c r="B16" t="n">
-        <v>98060</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Gullblanka, Vstm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>497332</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6621841</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Lindesberg</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Linde</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27725-2026 artfynd.xlsx
+++ b/artfynd/A 27725-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135031081</v>
+        <v>135023647</v>
       </c>
       <c r="B3" t="n">
         <v>57162</v>
@@ -816,24 +816,31 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497392</v>
+        <v>497636</v>
       </c>
       <c r="R3" t="n">
-        <v>6621831</v>
+        <v>6621917</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +864,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:22</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:22</t>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fjäder från tjädertupp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,23 +885,38 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Våtmark med barrträd</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135031156</v>
+        <v>135031081</v>
       </c>
       <c r="B4" t="n">
         <v>57162</v>
@@ -930,7 +947,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497439</v>
+        <v>497392</v>
       </c>
       <c r="R4" t="n">
-        <v>6621865</v>
+        <v>6621831</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På hällen</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1028,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135031182</v>
+        <v>135031156</v>
       </c>
       <c r="B5" t="n">
         <v>57162</v>
@@ -1044,24 +1056,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497444</v>
+        <v>497439</v>
       </c>
       <c r="R5" t="n">
-        <v>6621867</v>
+        <v>6621865</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1105,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1113,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillning och fjäder fr höna</t>
+          <t>På hällen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,7 +1145,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135031223</v>
+        <v>135031182</v>
       </c>
       <c r="B6" t="n">
         <v>57162</v>
@@ -1175,10 +1173,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1187,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497436</v>
+        <v>497444</v>
       </c>
       <c r="R6" t="n">
-        <v>6621916</v>
+        <v>6621867</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1222,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1244,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På häll</t>
+          <t>Spillning och fjäder fr höna</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,7 +1276,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135031358</v>
+        <v>135031223</v>
       </c>
       <c r="B7" t="n">
         <v>57162</v>
@@ -1304,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497502</v>
+        <v>497436</v>
       </c>
       <c r="R7" t="n">
-        <v>6621886</v>
+        <v>6621916</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1339,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1361,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På häll</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135031428</v>
+        <v>135031358</v>
       </c>
       <c r="B8" t="n">
         <v>57162</v>
@@ -1416,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497530</v>
+        <v>497502</v>
       </c>
       <c r="R8" t="n">
-        <v>6621896</v>
+        <v>6621886</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1451,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,12 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Vid rotvälta</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,7 +1505,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135031854</v>
+        <v>135031428</v>
       </c>
       <c r="B9" t="n">
         <v>57162</v>
@@ -1533,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497649</v>
+        <v>497530</v>
       </c>
       <c r="R9" t="n">
-        <v>6621782</v>
+        <v>6621896</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1568,7 +1580,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1590,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vid rotvälta</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,7 +1622,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135038922</v>
+        <v>135031854</v>
       </c>
       <c r="B10" t="n">
         <v>57162</v>
@@ -1634,34 +1651,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497369</v>
+        <v>497649</v>
       </c>
       <c r="R10" t="n">
-        <v>6622106</v>
+        <v>6621782</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1690,7 +1697,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,12 +1707,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Sandbad med honfjädrar</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,65 +1722,75 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135031276</v>
+        <v>135038922</v>
       </c>
       <c r="B11" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497469</v>
+        <v>497369</v>
       </c>
       <c r="R11" t="n">
-        <v>6621857</v>
+        <v>6622106</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1807,7 +1819,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1829,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sandbad med honfjädrar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,11 +1845,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1849,38 +1861,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135031098</v>
+        <v>135031276</v>
       </c>
       <c r="B12" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1889,13 +1901,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497399</v>
+        <v>497469</v>
       </c>
       <c r="R12" t="n">
-        <v>6621793</v>
+        <v>6621857</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,7 +1936,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1946,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135031702</v>
+        <v>135031098</v>
       </c>
       <c r="B13" t="n">
-        <v>8449</v>
+        <v>58131</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,42 +1989,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>103023</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497612</v>
+        <v>497399</v>
       </c>
       <c r="R13" t="n">
-        <v>6621778</v>
+        <v>6621793</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2041,7 +2053,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2051,12 +2063,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,54 +2074,59 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135031097</v>
+        <v>135031702</v>
       </c>
       <c r="B14" t="n">
-        <v>56706</v>
+        <v>8449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206046</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2123,10 +2135,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497411</v>
+        <v>497612</v>
       </c>
       <c r="R14" t="n">
-        <v>6621836</v>
+        <v>6621778</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2158,7 +2170,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2168,7 +2180,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,52 +2212,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134232854</v>
+        <v>135031097</v>
       </c>
       <c r="B15" t="n">
-        <v>98060</v>
+        <v>56706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>206046</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497332</v>
+        <v>497411</v>
       </c>
       <c r="R15" t="n">
-        <v>6621841</v>
+        <v>6621836</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2264,27 +2282,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,15 +2312,131 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134232854</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>497332</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6621841</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27725-2026 artfynd.xlsx
+++ b/artfynd/A 27725-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,10 +789,15 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135031673</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135023647</v>
+        <v>135031081</v>
       </c>
       <c r="B3" t="n">
         <v>57162</v>
@@ -816,31 +826,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497636</v>
+        <v>497392</v>
       </c>
       <c r="R3" t="n">
-        <v>6621917</v>
+        <v>6621831</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,17 +867,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fjäder från tjädertupp.</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,38 +893,28 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Våtmark med barrträd</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Hår, päls, fjäll eller fjädrar</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Hair, fur, scale or feather</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135031081</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135031081</v>
+        <v>135031156</v>
       </c>
       <c r="B4" t="n">
         <v>57162</v>
@@ -947,7 +945,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -956,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497392</v>
+        <v>497439</v>
       </c>
       <c r="R4" t="n">
-        <v>6621831</v>
+        <v>6621865</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -991,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På hällen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1028,15 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135031156</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135031156</v>
+        <v>135031182</v>
       </c>
       <c r="B5" t="n">
         <v>57162</v>
@@ -1056,10 +1064,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497439</v>
+        <v>497444</v>
       </c>
       <c r="R5" t="n">
-        <v>6621865</v>
+        <v>6621867</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1103,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,12 +1135,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På hällen</t>
+          <t>Spillning och fjäder fr höna</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1164,15 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135031182</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135031182</v>
+        <v>135031223</v>
       </c>
       <c r="B6" t="n">
         <v>57162</v>
@@ -1173,24 +1200,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1199,10 +1212,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497444</v>
+        <v>497436</v>
       </c>
       <c r="R6" t="n">
-        <v>6621867</v>
+        <v>6621916</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1234,7 +1247,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,12 +1257,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillning och fjäder fr höna</t>
+          <t>På häll</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,10 +1286,15 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135031223</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135031223</v>
+        <v>135031358</v>
       </c>
       <c r="B7" t="n">
         <v>57162</v>
@@ -1316,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497436</v>
+        <v>497502</v>
       </c>
       <c r="R7" t="n">
-        <v>6621916</v>
+        <v>6621886</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1351,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,12 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På häll</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,10 +1403,15 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135031358</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135031358</v>
+        <v>135031428</v>
       </c>
       <c r="B8" t="n">
         <v>57162</v>
@@ -1433,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497502</v>
+        <v>497530</v>
       </c>
       <c r="R8" t="n">
-        <v>6621886</v>
+        <v>6621896</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1468,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,7 +1496,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vid rotvälta</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,10 +1525,15 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135031428</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135031428</v>
+        <v>135031854</v>
       </c>
       <c r="B9" t="n">
         <v>57162</v>
@@ -1545,10 +1573,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497530</v>
+        <v>497649</v>
       </c>
       <c r="R9" t="n">
-        <v>6621896</v>
+        <v>6621782</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1580,7 +1608,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,12 +1618,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Vid rotvälta</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,10 +1642,15 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135031854</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135031854</v>
+        <v>135038922</v>
       </c>
       <c r="B10" t="n">
         <v>57162</v>
@@ -1651,24 +1679,34 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497649</v>
+        <v>497369</v>
       </c>
       <c r="R10" t="n">
-        <v>6621782</v>
+        <v>6622106</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1697,7 +1735,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1707,7 +1745,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sandbad med honfjädrar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,75 +1765,70 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135038922</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135038922</v>
+        <v>135031276</v>
       </c>
       <c r="B11" t="n">
-        <v>57162</v>
+        <v>58136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497369</v>
+        <v>497469</v>
       </c>
       <c r="R11" t="n">
-        <v>6622106</v>
+        <v>6621857</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1819,7 +1857,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1829,12 +1867,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Sandbad med honfjädrar</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,6 +1878,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1858,41 +1896,46 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135031276</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135031276</v>
+        <v>135031098</v>
       </c>
       <c r="B12" t="n">
-        <v>58136</v>
+        <v>58131</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>103023</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1901,13 +1944,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497469</v>
+        <v>497399</v>
       </c>
       <c r="R12" t="n">
-        <v>6621857</v>
+        <v>6621793</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1936,7 +1979,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1946,7 +1989,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,13 +2018,18 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135031098</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135031098</v>
+        <v>135031702</v>
       </c>
       <c r="B13" t="n">
-        <v>58131</v>
+        <v>8449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,42 +2037,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103023</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497399</v>
+        <v>497612</v>
       </c>
       <c r="R13" t="n">
-        <v>6621793</v>
+        <v>6621778</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2053,7 +2101,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,7 +2111,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,59 +2127,59 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135031702</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135031702</v>
+        <v>135031097</v>
       </c>
       <c r="B14" t="n">
-        <v>8449</v>
+        <v>56706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>206046</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2135,10 +2188,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497612</v>
+        <v>497411</v>
       </c>
       <c r="R14" t="n">
-        <v>6621778</v>
+        <v>6621836</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2170,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2180,12 +2233,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2209,56 +2257,60 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135031097</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135031097</v>
+        <v>134232854</v>
       </c>
       <c r="B15" t="n">
-        <v>56706</v>
+        <v>98060</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206046</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497411</v>
+        <v>497332</v>
       </c>
       <c r="R15" t="n">
-        <v>6621836</v>
+        <v>6621841</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2282,22 +2334,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,133 +2369,38 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>134232854</v>
-      </c>
-      <c r="B16" t="n">
-        <v>98060</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Gullblanka, Vstm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>497332</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6621841</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Lindesberg</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Linde</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232854</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27725-2026 artfynd.xlsx
+++ b/artfynd/A 27725-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135031673</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135031081</v>
+        <v>135023647</v>
       </c>
       <c r="B3" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,24 +826,31 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497392</v>
+        <v>497636</v>
       </c>
       <c r="R3" t="n">
-        <v>6621831</v>
+        <v>6621917</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +874,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:22</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:22</t>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fjäder från tjädertupp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,31 +895,46 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Våtmark med barrträd</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Hår, päls, fjäll eller fjädrar</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Hair, fur, scale or feather</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135031081</t>
+          <t>https://artportalen.se/Sighting/135023647</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135031156</v>
+        <v>135031081</v>
       </c>
       <c r="B4" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,7 +962,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497439</v>
+        <v>497392</v>
       </c>
       <c r="R4" t="n">
-        <v>6621865</v>
+        <v>6621831</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -989,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På hällen</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,16 +1042,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135031156</t>
+          <t>https://artportalen.se/Sighting/135031081</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135031182</v>
+        <v>135031156</v>
       </c>
       <c r="B5" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,24 +1076,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1090,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497444</v>
+        <v>497439</v>
       </c>
       <c r="R5" t="n">
-        <v>6621867</v>
+        <v>6621865</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1125,7 +1123,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,12 +1133,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillning och fjäder fr höna</t>
+          <t>På hällen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,16 +1164,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135031182</t>
+          <t>https://artportalen.se/Sighting/135031156</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135031223</v>
+        <v>135031182</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,10 +1198,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1212,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497436</v>
+        <v>497444</v>
       </c>
       <c r="R6" t="n">
-        <v>6621916</v>
+        <v>6621867</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1247,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1257,12 +1269,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På häll</t>
+          <t>Spillning och fjäder fr höna</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,16 +1300,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135031223</t>
+          <t>https://artportalen.se/Sighting/135031182</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135031358</v>
+        <v>135031223</v>
       </c>
       <c r="B7" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,10 +1346,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497502</v>
+        <v>497436</v>
       </c>
       <c r="R7" t="n">
-        <v>6621886</v>
+        <v>6621916</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1369,7 +1381,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1391,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På häll</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,16 +1422,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135031358</t>
+          <t>https://artportalen.se/Sighting/135031223</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135031428</v>
+        <v>135031358</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,10 +1468,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497530</v>
+        <v>497502</v>
       </c>
       <c r="R8" t="n">
-        <v>6621896</v>
+        <v>6621886</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1486,7 +1503,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,12 +1513,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Vid rotvälta</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,16 +1539,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135031428</t>
+          <t>https://artportalen.se/Sighting/135031358</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135031854</v>
+        <v>135031428</v>
       </c>
       <c r="B9" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,10 +1585,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497649</v>
+        <v>497530</v>
       </c>
       <c r="R9" t="n">
-        <v>6621782</v>
+        <v>6621896</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1608,7 +1620,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1618,7 +1630,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vid rotvälta</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,16 +1661,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135031854</t>
+          <t>https://artportalen.se/Sighting/135031428</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135038922</v>
+        <v>135031854</v>
       </c>
       <c r="B10" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,34 +1696,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497369</v>
+        <v>497649</v>
       </c>
       <c r="R10" t="n">
-        <v>6622106</v>
+        <v>6621782</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1735,7 +1742,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1745,12 +1752,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Sandbad med honfjädrar</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,70 +1767,80 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135038922</t>
+          <t>https://artportalen.se/Sighting/135031854</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135031276</v>
+        <v>135038922</v>
       </c>
       <c r="B11" t="n">
-        <v>58136</v>
+        <v>57167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Lindes sn, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497469</v>
+        <v>497369</v>
       </c>
       <c r="R11" t="n">
-        <v>6621857</v>
+        <v>6622106</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1857,7 +1869,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1867,7 +1879,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sandbad med honfjädrar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1878,11 +1895,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1898,44 +1910,44 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135031276</t>
+          <t>https://artportalen.se/Sighting/135038922</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135031098</v>
+        <v>135031276</v>
       </c>
       <c r="B12" t="n">
-        <v>58131</v>
+        <v>58141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1944,13 +1956,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497399</v>
+        <v>497469</v>
       </c>
       <c r="R12" t="n">
-        <v>6621793</v>
+        <v>6621857</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1979,7 +1991,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1989,7 +2001,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,16 +2032,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135031098</t>
+          <t>https://artportalen.se/Sighting/135031276</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135031702</v>
+        <v>135031098</v>
       </c>
       <c r="B13" t="n">
-        <v>8449</v>
+        <v>58136</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,42 +2049,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>103023</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Slöjdarkullen, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497612</v>
+        <v>497399</v>
       </c>
       <c r="R13" t="n">
-        <v>6621778</v>
+        <v>6621793</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2101,7 +2113,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2111,12 +2123,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2127,59 +2134,64 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135031702</t>
+          <t>https://artportalen.se/Sighting/135031098</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135031097</v>
+        <v>135031702</v>
       </c>
       <c r="B14" t="n">
-        <v>56706</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206046</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2188,10 +2200,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497411</v>
+        <v>497612</v>
       </c>
       <c r="R14" t="n">
-        <v>6621836</v>
+        <v>6621778</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2223,7 +2235,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,7 +2245,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2259,58 +2276,59 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135031097</t>
+          <t>https://artportalen.se/Sighting/135031702</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134232854</v>
+        <v>135031097</v>
       </c>
       <c r="B15" t="n">
-        <v>98060</v>
+        <v>56711</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>206046</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497332</v>
+        <v>497411</v>
       </c>
       <c r="R15" t="n">
-        <v>6621841</v>
+        <v>6621836</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2334,27 +2352,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,16 +2382,137 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135031097</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134232854</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>497332</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6621841</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134232854</t>
         </is>
@@ -2400,6 +2534,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
